--- a/result.xlsx
+++ b/result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intern\VCCorp\NRMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925063B7-C0AB-42B0-BD0A-BFB556B61DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{299071DA-8373-4D00-BFCA-2EDBD9DB70C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1E33EB1C-A5B9-4445-B58A-97AD2F87709D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="12">
   <si>
     <t>negative_sampling_ratio</t>
   </si>
@@ -62,21 +62,6 @@
     <t>ndcg10_test</t>
   </si>
   <si>
-    <t>2026-08-19_10-43-39</t>
-  </si>
-  <si>
-    <t>2026-09-04_10-04-02</t>
-  </si>
-  <si>
-    <t>2026-09-04_10-16-19</t>
-  </si>
-  <si>
-    <t>2026-09-04_10-42-47</t>
-  </si>
-  <si>
-    <t>2026-09-04_10-57-59</t>
-  </si>
-  <si>
     <t>STT</t>
   </si>
   <si>
@@ -84,9 +69,6 @@
   </si>
   <si>
     <t>Metrics</t>
-  </si>
-  <si>
-    <t>Experiments</t>
   </si>
   <si>
     <t>Seed</t>
@@ -100,8 +82,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="180" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="183" formatCode="0.000000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.000000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -152,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -201,11 +183,119 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -225,6 +315,63 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -234,19 +381,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -583,380 +727,473 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4473608D-3B7C-4CDD-B44A-AB446196785E}">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultColWidth="7.109375" defaultRowHeight="16.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="9.109375" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.109375" style="10"/>
-    <col min="11" max="11" width="7.109375" style="1"/>
-    <col min="12" max="12" width="4.44140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="6" style="1" customWidth="1"/>
-    <col min="14" max="17" width="22.33203125" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="7.109375" style="1"/>
+    <col min="2" max="4" width="9.109375" style="1" customWidth="1"/>
+    <col min="5" max="8" width="13.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" style="7"/>
+    <col min="10" max="10" width="7.109375" style="1"/>
+    <col min="11" max="11" width="4.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6" style="1" customWidth="1"/>
+    <col min="13" max="20" width="12.6640625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="7.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="L1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="7">
+    <row r="1" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="K1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="25"/>
+      <c r="O1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="R1" s="25"/>
+      <c r="S1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" s="25"/>
+    </row>
+    <row r="2" spans="1:20" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28"/>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="26"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="9">
         <v>200</v>
       </c>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7">
+      <c r="N2" s="23">
         <v>256</v>
       </c>
-      <c r="Q1" s="7"/>
+      <c r="O2" s="9">
+        <v>200</v>
+      </c>
+      <c r="P2" s="23">
+        <v>256</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>200</v>
+      </c>
+      <c r="R2" s="23">
+        <v>256</v>
+      </c>
+      <c r="S2" s="9">
+        <v>200</v>
+      </c>
+      <c r="T2" s="13">
+        <v>256</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
+      <c r="B3" s="2">
+        <v>4</v>
       </c>
       <c r="C3" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="E3" s="2">
-        <v>200</v>
+        <v>0.37724819059724501</v>
       </c>
       <c r="F3" s="2">
+        <v>0.44033336210629798</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.32878496787497402</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.39442231624937302</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
+      </c>
+      <c r="L3" s="12">
+        <v>42</v>
+      </c>
+      <c r="M3" s="14">
         <v>0.37724819059724501</v>
       </c>
-      <c r="G3" s="2">
+      <c r="N3" s="8">
+        <v>0.38072596085108701</v>
+      </c>
+      <c r="O3" s="17">
         <v>0.44033336210629798</v>
       </c>
-      <c r="H3" s="2">
+      <c r="P3" s="8">
+        <v>0.44275749054083602</v>
+      </c>
+      <c r="Q3" s="14">
         <v>0.32878496787497402</v>
       </c>
-      <c r="I3" s="2">
+      <c r="R3" s="8">
+        <v>0.33072823253623201</v>
+      </c>
+      <c r="S3" s="14">
         <v>0.39442231624937302</v>
       </c>
-      <c r="J3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1</v>
-      </c>
-      <c r="M3" s="11">
-        <v>42</v>
-      </c>
-      <c r="N3" s="12">
-        <v>0.32878496787497402</v>
-      </c>
-      <c r="O3" s="12">
-        <v>0.39442231624937302</v>
-      </c>
-      <c r="P3" s="12">
-        <v>0.33072823253623201</v>
-      </c>
-      <c r="Q3" s="12">
+      <c r="T3" s="16">
         <v>0.394103817508617</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
+      <c r="B4" s="2">
+        <v>4</v>
       </c>
       <c r="C4" s="2">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2">
         <v>16</v>
       </c>
-      <c r="E4" s="4">
+      <c r="D4" s="4">
         <v>256</v>
       </c>
+      <c r="E4" s="5">
+        <v>0.38072596085108701</v>
+      </c>
       <c r="F4" s="5">
-        <v>0.38072596085108701</v>
+        <v>0.44275749054083602</v>
       </c>
       <c r="G4" s="5">
-        <v>0.44275749054083602</v>
-      </c>
-      <c r="H4" s="5">
         <v>0.33072823253623201</v>
       </c>
-      <c r="I4" s="6">
+      <c r="H4" s="6">
         <v>0.394103817508617</v>
       </c>
-      <c r="J4" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="I4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="2">
         <v>2</v>
       </c>
-      <c r="M4" s="11">
+      <c r="L4" s="12">
         <v>43</v>
       </c>
-      <c r="N4" s="12">
+      <c r="M4" s="17">
+        <v>0.37814730683730902</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.37800657891981898</v>
+      </c>
+      <c r="O4" s="17">
+        <v>0.44238614725472902</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0.44114325234433599</v>
+      </c>
+      <c r="Q4" s="14">
         <v>0.32378562779336001</v>
       </c>
-      <c r="O4" s="12">
+      <c r="R4" s="8">
+        <v>0.32261855194435801</v>
+      </c>
+      <c r="S4" s="14">
         <v>0.38849435965678297</v>
       </c>
-      <c r="P4" s="12">
-        <v>0.32261855194435801</v>
-      </c>
-      <c r="Q4" s="12">
+      <c r="T4" s="16">
         <v>0.38894600972325999</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+      <c r="B5" s="2">
+        <v>4</v>
       </c>
       <c r="C5" s="2">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2">
         <v>16</v>
       </c>
-      <c r="E5" s="4">
+      <c r="D5" s="4">
         <v>300</v>
       </c>
+      <c r="E5" s="6">
+        <v>0.37574293387616797</v>
+      </c>
       <c r="F5" s="6">
-        <v>0.37574293387616797</v>
+        <v>0.43958171369187099</v>
       </c>
       <c r="G5" s="6">
-        <v>0.43958171369187099</v>
+        <v>0.32831164892047598</v>
       </c>
       <c r="H5" s="6">
-        <v>0.32831164892047598</v>
-      </c>
-      <c r="I5" s="6">
         <v>0.39266605562283802</v>
       </c>
-      <c r="L5" s="2">
+      <c r="K5" s="2">
         <v>3</v>
       </c>
-      <c r="M5" s="11">
+      <c r="L5" s="12">
         <v>44</v>
       </c>
-      <c r="N5" s="12">
+      <c r="M5" s="17">
+        <v>0.37541108094748499</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0.38119901038854798</v>
+      </c>
+      <c r="O5" s="17">
+        <v>0.43810607603901802</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0.44308655396114199</v>
+      </c>
+      <c r="Q5" s="14">
         <v>0.32651205142309497</v>
       </c>
-      <c r="O5" s="12">
+      <c r="R5" s="8">
+        <v>0.32868400993232699</v>
+      </c>
+      <c r="S5" s="14">
         <v>0.39166365777331902</v>
       </c>
-      <c r="P5" s="12">
-        <v>0.32868400993232699</v>
-      </c>
-      <c r="Q5" s="12">
+      <c r="T5" s="16">
         <v>0.39219788313420401</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="D6" s="4">
+      <c r="C6" s="4">
         <v>32</v>
       </c>
-      <c r="E6" s="2">
+      <c r="D6" s="2">
         <v>200</v>
       </c>
+      <c r="E6" s="6">
+        <v>0.37701771367886799</v>
+      </c>
       <c r="F6" s="6">
-        <v>0.37701771367886799</v>
+        <v>0.44029417735506399</v>
       </c>
       <c r="G6" s="6">
-        <v>0.44029417735506399</v>
+        <v>0.32287513877040802</v>
       </c>
       <c r="H6" s="6">
-        <v>0.32287513877040802</v>
-      </c>
-      <c r="I6" s="6">
         <v>0.38814509108803003</v>
       </c>
-      <c r="L6" s="2">
+      <c r="K6" s="2">
         <v>4</v>
       </c>
-      <c r="M6" s="11">
+      <c r="L6" s="12">
         <v>45</v>
       </c>
-      <c r="N6" s="12">
+      <c r="M6" s="17">
+        <v>0.37486665307682299</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0.37777800771266801</v>
+      </c>
+      <c r="O6" s="17">
+        <v>0.43731061110337999</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0.44033347185994298</v>
+      </c>
+      <c r="Q6" s="14">
         <v>0.32985695450074998</v>
       </c>
-      <c r="O6" s="12">
+      <c r="R6" s="8">
+        <v>0.327809474055275</v>
+      </c>
+      <c r="S6" s="14">
         <v>0.39326396503592398</v>
       </c>
-      <c r="P6" s="12">
-        <v>0.327809474055275</v>
-      </c>
-      <c r="Q6" s="12">
+      <c r="T6" s="16">
         <v>0.39294038220277899</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4">
+      <c r="B7" s="4">
         <v>8</v>
       </c>
+      <c r="C7" s="2">
+        <v>16</v>
+      </c>
       <c r="D7" s="2">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2">
         <v>200</v>
       </c>
+      <c r="E7" s="6">
+        <v>0.37230499007844198</v>
+      </c>
       <c r="F7" s="6">
-        <v>0.37230499007844198</v>
+        <v>0.43623413301530301</v>
       </c>
       <c r="G7" s="6">
-        <v>0.43623413301530301</v>
+        <v>0.32641405958710801</v>
       </c>
       <c r="H7" s="6">
-        <v>0.32641405958710801</v>
-      </c>
-      <c r="I7" s="6">
         <v>0.391578205806557</v>
       </c>
-      <c r="L7" s="2">
+      <c r="K7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="11">
+      <c r="L7" s="12">
         <v>46</v>
       </c>
-      <c r="N7" s="12">
+      <c r="M7" s="18">
+        <v>0.37586248018773299</v>
+      </c>
+      <c r="N7" s="19">
+        <v>0.380316812719867</v>
+      </c>
+      <c r="O7" s="20">
+        <v>0.43899569466952199</v>
+      </c>
+      <c r="P7" s="19">
+        <v>0.44253978405981698</v>
+      </c>
+      <c r="Q7" s="10">
         <v>0.32079712918512399</v>
       </c>
-      <c r="O7" s="12">
+      <c r="R7" s="19">
+        <v>0.32644081508008799</v>
+      </c>
+      <c r="S7" s="10">
         <v>0.387163174496167</v>
       </c>
-      <c r="P7" s="12">
-        <v>0.32644081508008799</v>
-      </c>
-      <c r="Q7" s="12">
+      <c r="T7" s="11">
         <v>0.390763518522449</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N8" s="13">
-        <f>AVERAGE(N3:N7)</f>
+    <row r="8" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="30">
+        <f>AVERAGE(M3:M7)</f>
+        <v>0.376307142329319</v>
+      </c>
+      <c r="N8" s="15">
+        <f t="shared" ref="N8:T8" si="0">AVERAGE(N3:N7)</f>
+        <v>0.37960527411839778</v>
+      </c>
+      <c r="O8" s="30">
+        <f t="shared" si="0"/>
+        <v>0.43942637823458941</v>
+      </c>
+      <c r="P8" s="15">
+        <f t="shared" ref="P8:T8" si="1">AVERAGE(P3:P7)</f>
+        <v>0.44197211055321473</v>
+      </c>
+      <c r="Q8" s="30">
+        <f t="shared" si="1"/>
         <v>0.32594734615546062</v>
       </c>
-      <c r="O8" s="13">
-        <f t="shared" ref="O8:Q8" si="0">AVERAGE(O3:O7)</f>
+      <c r="R8" s="15">
+        <f t="shared" si="1"/>
+        <v>0.32725621670965599</v>
+      </c>
+      <c r="S8" s="30">
+        <f t="shared" si="1"/>
         <v>0.39100149464231315</v>
       </c>
-      <c r="P8" s="13">
-        <f t="shared" si="0"/>
-        <v>0.32725621670965599</v>
-      </c>
-      <c r="Q8" s="13">
-        <f t="shared" si="0"/>
+      <c r="T8" s="15">
+        <f t="shared" si="1"/>
         <v>0.39179032221826182</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="N9" s="14">
-        <f>_xlfn.STDEV.S(N3:N7)</f>
+    <row r="9" spans="1:20" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="21">
+        <f>_xlfn.STDEV.S(M3:M7)</f>
+        <v>1.3553078032096017E-3</v>
+      </c>
+      <c r="N9" s="32">
+        <f t="shared" ref="N9:T9" si="2">_xlfn.STDEV.S(N3:N7)</f>
+        <v>1.5966331833318984E-3</v>
+      </c>
+      <c r="O9" s="31">
+        <f t="shared" si="2"/>
+        <v>1.9992504326918148E-3</v>
+      </c>
+      <c r="P9" s="22">
+        <f t="shared" ref="P9:T9" si="3">_xlfn.STDEV.S(P3:P7)</f>
+        <v>1.1782616159028152E-3</v>
+      </c>
+      <c r="Q9" s="31">
+        <f t="shared" si="3"/>
         <v>3.7031671442999559E-3</v>
       </c>
-      <c r="O9" s="14">
-        <f>_xlfn.STDEV.S(O3:O7)</f>
+      <c r="R9" s="22">
+        <f t="shared" si="3"/>
+        <v>3.0237557511301051E-3</v>
+      </c>
+      <c r="S9" s="31">
+        <f t="shared" si="3"/>
         <v>3.0934479202557106E-3</v>
       </c>
-      <c r="P9" s="14">
-        <f>_xlfn.STDEV.S(P3:P7)</f>
-        <v>3.0237557511301051E-3</v>
-      </c>
-      <c r="Q9" s="14">
-        <f t="shared" ref="O9:Q9" si="1">_xlfn.STDEV.S(Q3:Q7)</f>
+      <c r="T9" s="22">
+        <f t="shared" si="3"/>
         <v>1.9990900258395877E-3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="B1:B2"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="M1:M2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:H1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
